--- a/04_DESIGN_TABLES/DesignTable_1504.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1504.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -599,6 +604,9 @@
       <c r="I4" t="n">
         <v>0.54</v>
       </c>
+      <c r="J4" t="n">
+        <v>0.54</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>1504-04-04-FG</t>
@@ -611,12 +619,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Air-Way s144 only (double-pass 11 rows)</t>
+          <t>Air-Way s144 only (double-pass 11 rows) | THDMAJ_A1 0.54 = end library -04 (Air-Way printed "1/4918"; Q-TRANSFER-ENDLIB = yes; PROPOSAL, genfeat ANGLED 2026-10-18)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1217,24 +1225,56 @@
           <t>1504-06-06-FG</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.675</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>1504-06-06-FG</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 3/8-18 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1504-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1504-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1504-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1504-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1245,6 +1285,11 @@
       <c r="Q14" t="inlineStr">
         <is>
           <t>1504-06-06-FG</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1254,24 +1299,56 @@
           <t>1504-20-20-FG</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.66</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>1504-20-20-FG</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A NPTF) x 1 1/4-11 1/2 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_b/1504-20-20-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 a9d438ebfceb29dc...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1282,6 +1359,11 @@
       <c r="Q15" t="inlineStr">
         <is>
           <t>1504-20-20-FG</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
@@ -1356,6 +1438,228 @@
       <c r="Q17" t="inlineStr">
         <is>
           <t>1504-32-32-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1504-08-08-FG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1504-08-08-FG</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1/2-14 (A NPTF) x 1/2-14 (A1 NPSM)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1504-08-08-FG</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1504-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1504-12-12-FG</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF) x 3/4-14 (A1 NPSM)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1504-12-12-FG</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1504-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1504-16-16-FG</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A NPTF) x 1-11 1/2 (A1 NPSM)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1504-16-16-FG</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_1504.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1504.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,11 @@
           <t>$PRP@DimSource</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>PORTDEPTH@BORE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1486,17 +1491,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library | 2026-10-20 (batch 19 D_geom): DataStatus MISSING -&gt; ASSUMED - one source (Brennan TFA catalog p.22 TFA-p022-t01); generated with the batch-17 1504 SPEC; D@BORE = Brennan A2 DRILL - flag: OMi's 2026-10-18 drawings of sibling 1504 sizes print the stem bore 0.01-0.02 below the Brennan drill on 7 of 7 bores (wave2 tee_elbow), so the true bore may be slightly smaller | PORTDEPTH 0.75 = Brennan port depth -08 = 0.750 (Brennan 1502 / 2505 / 2606 / 5502 / 5504 / 5505 / 5603 / 5605 / 5652 -08 STEPs and 5 more) (brennan_port_depths_out.txt) - Q-ANGLED-P1 settled from the Brennan STEPs 2026-10-18 (the MS51503 P1 library value does not fit the 45 deg female leg)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN | 2026-10-20: DataStatus MISSING -&gt; ASSUMED (Brennan catalog only; 1504 / 6807 SPEC exists since batch 17)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1513,6 +1518,9 @@
         <is>
           <t>BRENNAN</t>
         </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="19">
@@ -1560,17 +1568,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library | 2026-10-20 (batch 19 D_geom): DataStatus MISSING -&gt; ASSUMED - one source (Brennan TFA catalog p.22 TFA-p022-t01); generated with the batch-17 1504 SPEC; D@BORE = Brennan A2 DRILL - flag: OMi's 2026-10-18 drawings of sibling 1504 sizes print the stem bore 0.01-0.02 below the Brennan drill on 7 of 7 bores (wave2 tee_elbow), so the true bore may be slightly smaller</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN | 2026-10-20: DataStatus MISSING -&gt; ASSUMED (Brennan catalog only; 1504 / 6807 SPEC exists since batch 17)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1634,17 +1642,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library | 2026-10-20 (batch 19 D_geom): DataStatus MISSING -&gt; ASSUMED - one source (Brennan TFA catalog p.22 TFA-p022-t01); generated with the batch-17 1504 SPEC; D@BORE = Brennan A2 DRILL - flag: OMi's 2026-10-18 drawings of sibling 1504 sizes print the stem bore 0.01-0.02 below the Brennan drill on 7 of 7 bores (wave2 tee_elbow), so the true bore may be slightly smaller | PORTDEPTH 0.94 = Brennan port depth -16 = 0.940 (Brennan 5405-16-16, 5502-16-16-FG, 5503-16-16-FG STEPs) (brennan_port_depths_out.txt) - Q-ANGLED-P1 settled from the Brennan STEPs 2026-10-18 (the MS51503 P1 library value does not fit the 45 deg female leg)</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN | 2026-10-20: DataStatus MISSING -&gt; ASSUMED (Brennan catalog only; 1504 / 6807 SPEC exists since batch 17)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1661,6 +1669,9 @@
         <is>
           <t>BRENNAN</t>
         </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
